--- a/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/接待申请单.xlsx
+++ b/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/接待申请单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aLJD\server\oa\dh-oa\dh-module-oa\dh-module-oa-server\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{809971E2-9373-4C29-AAA5-E7FF9BE09F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E5028EE-C3B1-40A5-996A-0C2C97E6B64C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="3015" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
@@ -63,40 +63,35 @@
     <t>审批</t>
   </si>
   <si>
-    <t xml:space="preserve">	
-{cause}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">	
-{creatorName}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>{diningTime}</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">	
-{diningStandard}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">	
-{guestCount}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>{accompanyCount}</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">	
-{estimatedCost}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>{year}年{month}月{day}日</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{cause}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{creatorName}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{guestCount}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{estimatedCost}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{diningStandard}</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -241,6 +236,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -250,6 +248,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -258,12 +259,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -550,66 +545,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
     </row>
     <row r="2" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
     </row>
     <row r="3" spans="1:4" ht="29.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>10</v>
+      <c r="B3" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>11</v>
+      <c r="D3" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>12</v>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>13</v>
+      <c r="D4" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>14</v>
+      <c r="B5" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>15</v>
+      <c r="D5" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -621,17 +616,17 @@
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="6"/>
     </row>
     <row r="8" spans="1:4" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
+      <c r="A8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/接待申请单.xlsx
+++ b/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/接待申请单.xlsx
@@ -1,32 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aLJD\server\oa\dh-oa\dh-module-oa\dh-module-oa-server\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E5028EE-C3B1-40A5-996A-0C2C97E6B64C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B5218F-4EC0-4675-817B-047D31EB0147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="3015" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -39,60 +28,52 @@
     <t>申请事由</t>
   </si>
   <si>
+    <t>{cause}</t>
+  </si>
+  <si>
     <t>申请人</t>
   </si>
   <si>
+    <t>{creatorName}</t>
+  </si>
+  <si>
     <t>就餐时间</t>
   </si>
   <si>
+    <t>{diningTime}</t>
+  </si>
+  <si>
     <t>就餐标准</t>
   </si>
   <si>
+    <t>{diningStandard}</t>
+  </si>
+  <si>
     <t>来宾人数</t>
   </si>
   <si>
+    <t>{guestCount}</t>
+  </si>
+  <si>
     <t>陪同人数</t>
   </si>
   <si>
+    <t>{accompanyCount}</t>
+  </si>
+  <si>
     <t>预估费用</t>
   </si>
   <si>
+    <t>{estimatedCost}</t>
+  </si>
+  <si>
     <t>审核</t>
   </si>
   <si>
     <t>审批</t>
   </si>
   <si>
-    <t>{diningTime}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{accompanyCount}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>{year}年{month}月{day}日</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{cause}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{creatorName}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{guestCount}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{estimatedCost}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>{diningStandard}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -120,18 +101,17 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -142,7 +122,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -175,49 +155,27 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <left/>
       <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -233,33 +191,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -538,103 +488,103 @@
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.375" customWidth="1"/>
-    <col min="2" max="2" width="38.75" customWidth="1"/>
-    <col min="3" max="3" width="13.125" customWidth="1"/>
-    <col min="4" max="4" width="15.125" customWidth="1"/>
+    <col min="1" max="1" width="14.375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="38.75" style="3" customWidth="1"/>
+    <col min="3" max="3" width="13.125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
     </row>
     <row r="2" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
     </row>
     <row r="3" spans="1:4" ht="29.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>13</v>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>14</v>
+        <v>3</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>17</v>
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2"/>
+      <c r="D6" s="4"/>
     </row>
     <row r="7" spans="1:4" ht="39.4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="4"/>
+      <c r="A7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="5"/>
       <c r="C7" s="5"/>
-      <c r="D7" s="6"/>
+      <c r="D7" s="5"/>
     </row>
     <row r="8" spans="1:4" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
+      <c r="A8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="A8:D8"/>
     <mergeCell ref="B7:D7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A1:D2"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.59055118110236204" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/接待申请单.xlsx
+++ b/dh-module-oa/dh-module-oa-server/src/main/resources/excel-templates/接待申请单.xlsx
@@ -1,21 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aLJD\server\oa\dh-oa\dh-module-oa\dh-module-oa-server\src\main\resources\excel-templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B5218F-4EC0-4675-817B-047D31EB0147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E5028EE-C3B1-40A5-996A-0C2C97E6B64C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="3015" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -28,52 +39,60 @@
     <t>申请事由</t>
   </si>
   <si>
+    <t>申请人</t>
+  </si>
+  <si>
+    <t>就餐时间</t>
+  </si>
+  <si>
+    <t>就餐标准</t>
+  </si>
+  <si>
+    <t>来宾人数</t>
+  </si>
+  <si>
+    <t>陪同人数</t>
+  </si>
+  <si>
+    <t>预估费用</t>
+  </si>
+  <si>
+    <t>审核</t>
+  </si>
+  <si>
+    <t>审批</t>
+  </si>
+  <si>
+    <t>{diningTime}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{accompanyCount}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{year}年{month}月{day}日</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>{cause}</t>
-  </si>
-  <si>
-    <t>申请人</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>{creatorName}</t>
-  </si>
-  <si>
-    <t>就餐时间</t>
-  </si>
-  <si>
-    <t>{diningTime}</t>
-  </si>
-  <si>
-    <t>就餐标准</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{guestCount}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{estimatedCost}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>{diningStandard}</t>
-  </si>
-  <si>
-    <t>来宾人数</t>
-  </si>
-  <si>
-    <t>{guestCount}</t>
-  </si>
-  <si>
-    <t>陪同人数</t>
-  </si>
-  <si>
-    <t>{accompanyCount}</t>
-  </si>
-  <si>
-    <t>预估费用</t>
-  </si>
-  <si>
-    <t>{estimatedCost}</t>
-  </si>
-  <si>
-    <t>审核</t>
-  </si>
-  <si>
-    <t>审批</t>
-  </si>
-  <si>
-    <t>{year}年{month}月{day}日</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -101,17 +120,18 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -122,7 +142,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -155,18 +175,31 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -176,6 +209,15 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -191,25 +233,33 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -488,103 +538,103 @@
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="38.75" style="3" customWidth="1"/>
-    <col min="3" max="3" width="13.125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="15.125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="14.375" customWidth="1"/>
+    <col min="2" max="2" width="38.75" customWidth="1"/>
+    <col min="3" max="3" width="13.125" customWidth="1"/>
+    <col min="4" max="4" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
     </row>
     <row r="2" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
     </row>
     <row r="3" spans="1:4" ht="29.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>4</v>
+      <c r="D3" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="C6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4" ht="39.4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="5"/>
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="4"/>
       <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
+      <c r="D7" s="6"/>
     </row>
     <row r="8" spans="1:4" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
+      <c r="A8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="A8:D8"/>
     <mergeCell ref="A1:D2"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B7:D7"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.59055118110236204" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" orientation="portrait"/>
